--- a/503020-budget-tracker.xlsx
+++ b/503020-budget-tracker.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
   <si>
     <t xml:space="preserve">50/30/20 Budget Tracker — How To Use</t>
   </si>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">Step 5 — Add Your Savings</t>
   </si>
   <si>
-    <t xml:space="preserve">Go to the Savings sheet. Enter each savings contribution. This includes: emergency fund deposits, 401(k)/RRSP, IRA/TFSA, FHSA, investment accounts, and any extra debt payments above the minimum.</t>
+    <t xml:space="preserve">Go to the Savings sheet. Enter each savings contribution. This includes: emergency fund deposits, RRSP or group RRSP, TFSA, FHSA, RESP, investment accounts, and any extra debt payments above the minimum.</t>
   </si>
   <si>
     <t xml:space="preserve">Step 6 — Review Your Report</t>
@@ -77,26 +77,28 @@
     <t xml:space="preserve">The 50/30/20 split is a guideline — not a rigid rule. If your needs consistently exceed 50% due to high housing costs, try a 60/20/20 or 70/20/10 split. Adjust the percentages in cells B11, B12, B13 on the Monthly Tracker sheet — they must add up to 100%.</t>
   </si>
   <si>
-    <t xml:space="preserve">US vs Canadian Savings Accounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US savers: prioritise employer 401(k) match, then Roth IRA, then HYSA emergency fund.
-Canadian savers: prioritise employer RRSP match, then FHSA (first-time buyers), then TFSA.
-Both: always capture free employer matching first — it is an immediate 50-100% return.</t>
+    <t xml:space="preserve">Where Your 20% Should Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A common order for Canadians:
+1. A starter emergency fund (at least one month of essential expenses).
+2. Any employer RRSP or pension match. It is an immediate, guaranteed return.
+3. High-interest debt such as credit cards.
+4. The FHSA, if you are a first-time home buyer.
+5. RRSP or TFSA, depending on whether your tax rate is higher now or in retirement.
+Full guide: 503020.ca/tfsa-rrsp-fhsa-where-your-20-goes.html</t>
   </si>
   <si>
     <t xml:space="preserve">Need Help?</t>
   </si>
   <si>
-    <t xml:space="preserve">Visit 503020.ca for the free online calculator and spending tracker.
-Visit vaultgoal.com to track savings goals.
-Visit debtcrusher.ca for debt payoff planning (Snowball vs Avalanche).
-Visit mortgagemasher.com for US mortgage calculations.
-Visit mortgagemasher.ca for Canadian mortgage calculations.
+    <t xml:space="preserve">Online budget calculator: 503020.ca
+Online spending tracker: 503020.ca/tracker.html
+Budgeting guides for Canadians: 503020.ca/guides.html
 All tools are free. No sign-up required.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sharpline · 503020.ca · Free personal finance tools for US and Canadian households · Not financial advice</t>
+    <t xml:space="preserve">Sharpline · 503020.ca · Free budgeting tools for Canadian households · Not financial advice</t>
   </si>
   <si>
     <t xml:space="preserve">50/30/20 Monthly Budget Tracker</t>
@@ -189,7 +191,7 @@
     <t xml:space="preserve">Groceries</t>
   </si>
   <si>
-    <t xml:space="preserve">Electricity</t>
+    <t xml:space="preserve">Hydro / Electricity</t>
   </si>
   <si>
     <t xml:space="preserve">Gas / Heating</t>
@@ -204,7 +206,7 @@
     <t xml:space="preserve">Mobile Phone</t>
   </si>
   <si>
-    <t xml:space="preserve">Health Insurance</t>
+    <t xml:space="preserve">Extended Health / Dental (if no plan)</t>
   </si>
   <si>
     <t xml:space="preserve">Car Payment</t>
@@ -240,6 +242,12 @@
     <t xml:space="preserve">Basic Clothing</t>
   </si>
   <si>
+    <t xml:space="preserve">Property Tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strata / Condo Fees</t>
+  </si>
+  <si>
     <t xml:space="preserve">Other Need</t>
   </si>
   <si>
@@ -315,19 +323,19 @@
     <t xml:space="preserve">Emergency Fund</t>
   </si>
   <si>
-    <t xml:space="preserve">401(k) / RRSP Contribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roth IRA / TFSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FHSA (Canada First-Home Savings)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">529 / RESP Education Savings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">General Investment Account</t>
+    <t xml:space="preserve">RRSP / Group RRSP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FHSA (First Home Savings Account)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESP (Education Savings)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Registered Investments</t>
   </si>
   <si>
     <t xml:space="preserve">Extra Credit Card Payment</t>
@@ -339,7 +347,7 @@
     <t xml:space="preserve">Down Payment Fund</t>
   </si>
   <si>
-    <t xml:space="preserve">Retirement (other)</t>
+    <t xml:space="preserve">Pension Top-Up / Other Retirement</t>
   </si>
   <si>
     <t xml:space="preserve">Sinking Fund — Car</t>
@@ -643,11 +651,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -676,7 +688,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -748,7 +760,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -804,7 +816,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -832,7 +844,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -860,7 +872,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1124,129 +1136,129 @@
   <dimension ref="A1:A35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+    <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+    <row r="15" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+    <row r="18" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+    <row r="21" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+    <row r="24" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+    <row r="27" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+    <row r="30" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+    <row r="33" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1270,252 +1282,252 @@
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <f aca="false">B11*B7</f>
         <v>2500</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <f aca="false">Needs!C36</f>
         <v>0</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">C11-D11</f>
         <v>2500</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="21" t="n">
         <f aca="false">B12*B7</f>
         <v>1500</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
         <f aca="false">Wants!C36</f>
         <v>0</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <f aca="false">C12-D12</f>
         <v>1500</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <f aca="false">B13*B7</f>
         <v>1000</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="26" t="n">
         <f aca="false">Savings!C36</f>
         <v>0</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">C13-D13</f>
         <v>1000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="27" t="n">
+      <c r="B14" s="27"/>
+      <c r="C14" s="28" t="n">
         <f aca="false">SUM(C11:C13)</f>
         <v>5000</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="28" t="n">
         <f aca="false">SUM(D11:D13)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="28" t="n">
         <f aca="false">SUM(E11:E13)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="28" t="n">
+      <c r="B17" s="29" t="n">
         <f aca="false">C11</f>
         <v>2500</v>
       </c>
-      <c r="C17" s="28" t="n">
+      <c r="C17" s="29" t="n">
         <f aca="false">D11</f>
         <v>0</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="30" t="n">
         <f aca="false">E11</f>
         <v>2500</v>
       </c>
-      <c r="E17" s="30" t="str">
+      <c r="E17" s="31" t="str">
         <f aca="false">IF(D11&lt;=C11*1.05,"✓ On Track","⚠ Over Budget")</f>
         <v>✓ On Track</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="28" t="n">
+      <c r="B18" s="29" t="n">
         <f aca="false">C12</f>
         <v>1500</v>
       </c>
-      <c r="C18" s="28" t="n">
+      <c r="C18" s="29" t="n">
         <f aca="false">D12</f>
         <v>0</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="30" t="n">
         <f aca="false">E12</f>
         <v>1500</v>
       </c>
-      <c r="E18" s="30" t="str">
+      <c r="E18" s="31" t="str">
         <f aca="false">IF(D12&lt;=C12*1.05,"✓ On Track","⚠ Over Budget")</f>
         <v>✓ On Track</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="28" t="n">
+      <c r="B19" s="29" t="n">
         <f aca="false">C13</f>
         <v>1000</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="29" t="n">
         <f aca="false">D13</f>
         <v>0</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="30" t="n">
         <f aca="false">E13</f>
         <v>1000</v>
       </c>
-      <c r="E19" s="30" t="str">
+      <c r="E19" s="31" t="str">
         <f aca="false">IF(D13&gt;=C13*0.9,"✓ On Track","↓ Below Target")</f>
         <v>↓ Below Target</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1545,246 +1557,250 @@
   <dimension ref="A1:C38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="34" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="35"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="38"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="35"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="36"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="38"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="35"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="36"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="38"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="39"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="36"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="39"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="36"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="36"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="38"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="34"/>
-      <c r="C24" s="35"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="38"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="35"/>
+      <c r="A26" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="36"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="38"/>
+      <c r="A27" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="39"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="35"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="36"/>
-      <c r="B29" s="37"/>
-      <c r="C29" s="38"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="39"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="35"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="36"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="38"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="35"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="36"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="38"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="35"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="36"/>
-      <c r="B35" s="37"/>
-      <c r="C35" s="38"/>
+      <c r="A35" s="37"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="39"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="39" t="s">
+      <c r="A36" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="40"/>
-      <c r="C36" s="41" t="n">
+      <c r="B36" s="41"/>
+      <c r="C36" s="42" t="n">
         <f aca="false">SUM(C6:C35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
+      <c r="A38" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1811,246 +1827,246 @@
   <dimension ref="A1:C38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
+      <c r="A2" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="44" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="44"/>
+      <c r="A6" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="45"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="45"/>
+      <c r="A7" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="38"/>
+      <c r="C7" s="46"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="44"/>
+      <c r="A8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="45"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="45"/>
+      <c r="A9" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="38"/>
+      <c r="C9" s="46"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="44"/>
+      <c r="A10" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="45"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="45"/>
+      <c r="A11" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="38"/>
+      <c r="C11" s="46"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="44"/>
+      <c r="A12" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="45"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="45"/>
+      <c r="A13" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="38"/>
+      <c r="C13" s="46"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="44"/>
+      <c r="A14" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="45"/>
+      <c r="A15" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="38"/>
+      <c r="C15" s="46"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="44"/>
+      <c r="A16" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="45"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="45"/>
+      <c r="A17" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="38"/>
+      <c r="C17" s="46"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="44"/>
+      <c r="A18" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="45"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="45"/>
+      <c r="A19" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="38"/>
+      <c r="C19" s="46"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="44"/>
+      <c r="A20" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="35"/>
+      <c r="C20" s="45"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="45"/>
+      <c r="A21" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="38"/>
+      <c r="C21" s="46"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="44"/>
+      <c r="A22" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="35"/>
+      <c r="C22" s="45"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="45"/>
+      <c r="A23" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="38"/>
+      <c r="C23" s="46"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24" s="34"/>
-      <c r="C24" s="44"/>
+      <c r="A24" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="35"/>
+      <c r="C24" s="45"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="45"/>
+      <c r="A25" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="46"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="44"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="45"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="36"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="45"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="46"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="44"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="45"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="36"/>
-      <c r="B29" s="37"/>
-      <c r="C29" s="45"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="46"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="44"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="45"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="36"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="45"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="46"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="44"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="45"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="36"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="45"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="46"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="44"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="45"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="36"/>
-      <c r="B35" s="37"/>
-      <c r="C35" s="45"/>
+      <c r="A35" s="37"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="46"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="46" t="s">
+      <c r="A36" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="47"/>
-      <c r="C36" s="48" t="n">
+      <c r="B36" s="48"/>
+      <c r="C36" s="49" t="n">
         <f aca="false">SUM(C6:C35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
+      <c r="A38" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2077,234 +2093,234 @@
   <dimension ref="A1:C38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
+      <c r="A2" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="51" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="51"/>
+      <c r="A6" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="52"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="52"/>
+      <c r="A7" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="38"/>
+      <c r="C7" s="53"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="51"/>
+      <c r="A8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="52"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="52"/>
+      <c r="A9" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="38"/>
+      <c r="C9" s="53"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="51"/>
+      <c r="A10" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="52"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="52"/>
+      <c r="A11" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="38"/>
+      <c r="C11" s="53"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="51"/>
+      <c r="A12" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="52"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="52"/>
+      <c r="A13" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="38"/>
+      <c r="C13" s="53"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="51"/>
+      <c r="A14" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="52"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="52"/>
+      <c r="A15" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" s="38"/>
+      <c r="C15" s="53"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="51"/>
+      <c r="A16" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="52"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="52"/>
+      <c r="A17" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="38"/>
+      <c r="C17" s="53"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="51"/>
+      <c r="A18" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="52"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="52"/>
+      <c r="A19" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="38"/>
+      <c r="C19" s="53"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="51"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="52"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="52"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="53"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="51"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="52"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="52"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="53"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="51"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="52"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="36"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="52"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="53"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="51"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="52"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="36"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="52"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="53"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="51"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="52"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="36"/>
-      <c r="B29" s="37"/>
-      <c r="C29" s="52"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="53"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="51"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="52"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="36"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="52"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="53"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="51"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="52"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="36"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="52"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="53"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="51"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="52"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="36"/>
-      <c r="B35" s="37"/>
-      <c r="C35" s="52"/>
+      <c r="A35" s="37"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="53"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="54"/>
-      <c r="C36" s="55" t="n">
+      <c r="B36" s="55"/>
+      <c r="C36" s="56" t="n">
         <f aca="false">SUM(C6:C35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
+      <c r="A38" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="3">
